--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487590_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487590_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. VILLAMANDOS TORRES</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0299</v>
+        <v>8.325100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1851</v>
+        <v>6.8005</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8448</v>
+        <v>1.5246</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3838</v>
+        <v>7.6531</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1192</v>
+        <v>2.643</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2646</v>
+        <v>5.0101</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9686</v>
+        <v>8.267300000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2378</v>
+        <v>3.2461</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7307</v>
+        <v>5.0213</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4152</v>
+        <v>-0.6142</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1187</v>
+        <v>-0.6031</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5339</v>
+        <v>-0.0111</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1402</v>
+        <v>0.4183</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4569</v>
+        <v>0.2198</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6833</v>
+        <v>0.1985</v>
       </c>
       <c r="V2" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7298</v>
+        <v>1.2239</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>M. VILLAMANDOS TORRES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8097</v>
+        <v>6.9443</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3395</v>
+        <v>6.3448</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4701</v>
+        <v>0.5995</v>
       </c>
       <c r="G3" t="n">
-        <v>7.6531</v>
+        <v>4.3838</v>
       </c>
       <c r="H3" t="n">
-        <v>2.643</v>
+        <v>3.1192</v>
       </c>
       <c r="I3" t="n">
-        <v>5.0101</v>
+        <v>1.2646</v>
       </c>
       <c r="J3" t="n">
-        <v>8.267300000000001</v>
+        <v>3.9686</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2461</v>
+        <v>3.2378</v>
       </c>
       <c r="L3" t="n">
-        <v>5.0213</v>
+        <v>0.7307</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6142</v>
+        <v>0.4152</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6031</v>
+        <v>-0.1187</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0111</v>
+        <v>0.5339</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.09710000000000001</v>
+        <v>1.0546</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2412</v>
+        <v>0.6166</v>
       </c>
       <c r="U3" t="n">
-        <v>0.144</v>
+        <v>0.438</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>2.7298</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.2774</v>
+        <v>6.6444</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4804</v>
+        <v>3.9018</v>
       </c>
       <c r="F4" t="n">
-        <v>2.797</v>
+        <v>2.7425</v>
       </c>
       <c r="G4" t="n">
         <v>4.028</v>
@@ -766,13 +766,13 @@
         <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9092</v>
+        <v>1.2761</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1346</v>
+        <v>0.556</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7746</v>
+        <v>0.7201</v>
       </c>
       <c r="V4" t="n">
         <v>0.5642</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8941</v>
+        <v>3.5965</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5282</v>
+        <v>3.1488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3659</v>
+        <v>0.4477</v>
       </c>
       <c r="G5" t="n">
         <v>3.2088</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0852</v>
+        <v>0.7876</v>
       </c>
       <c r="T5" t="n">
-        <v>0.729</v>
+        <v>0.3496</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3562</v>
+        <v>0.438</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1761</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6364</v>
+        <v>3.4601</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2794</v>
+        <v>2.9396</v>
       </c>
       <c r="F6" t="n">
-        <v>0.357</v>
+        <v>0.5205</v>
       </c>
       <c r="G6" t="n">
         <v>1.5529</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0074</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8625</v>
+        <v>0.5226</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1449</v>
+        <v>0.3084</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8346</v>
+        <v>2.3208</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8208</v>
+        <v>-0.5048</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6554</v>
+        <v>2.8256</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7927</v>
+        <v>0.4491</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7983</v>
+        <v>-1.1575</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.591</v>
+        <v>1.6066</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.39</v>
+        <v>-0.584</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4624</v>
+        <v>-1.2564</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8523</v>
+        <v>0.6724</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4027</v>
+        <v>1.0331</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6641</v>
+        <v>0.0989</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2614</v>
+        <v>0.9343</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2676</v>
+        <v>0.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2752</v>
+        <v>0.4374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.1626</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5537</v>
+        <v>1.2716</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2343</v>
+        <v>0.6119</v>
       </c>
       <c r="X7" t="n">
-        <v>1.3194</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1215</v>
+        <v>2.3094</v>
       </c>
       <c r="E8" t="n">
-        <v>1.38</v>
+        <v>1.5407</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7415</v>
+        <v>0.7687</v>
       </c>
       <c r="G8" t="n">
         <v>1.7758</v>
@@ -1078,13 +1078,13 @@
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3457</v>
+        <v>0.5336</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2557</v>
+        <v>0.4164</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09</v>
+        <v>0.1172</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9043</v>
+        <v>2.0193</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8001</v>
+        <v>0.8607</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1042</v>
+        <v>1.1587</v>
       </c>
       <c r="G9" t="n">
         <v>2.0468</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1575</v>
+        <v>0.2725</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2423</v>
+        <v>-0.1817</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3997</v>
+        <v>0.4542</v>
       </c>
       <c r="V9" t="n">
         <v>0.2821</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0779</v>
+        <v>1.8585</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3662</v>
+        <v>-1.3608</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4441</v>
+        <v>3.2193</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4491</v>
+        <v>-0.7927</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1575</v>
+        <v>0.7983</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6066</v>
+        <v>-1.591</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.584</v>
+        <v>-0.39</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2564</v>
+        <v>1.4624</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6724</v>
+        <v>-1.8523</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0331</v>
+        <v>-0.4027</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0989</v>
+        <v>-0.6641</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9343</v>
+        <v>0.2614</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6429</v>
+        <v>1.2915</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.424</v>
+        <v>0.7352</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2189</v>
+        <v>0.5563</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2716</v>
+        <v>1.5537</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6119</v>
+        <v>0.2343</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6597</v>
+        <v>1.3194</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4879</v>
+        <v>-1.23</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2856</v>
+        <v>-0.8642</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2022</v>
+        <v>-0.3658</v>
       </c>
       <c r="G11" t="n">
         <v>0.9166</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>0.897</v>
+        <v>1.1549</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1346</v>
+        <v>0.556</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7625</v>
+        <v>0.5989</v>
       </c>
       <c r="V11" t="n">
         <v>-3.1075</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0594</v>
+        <v>-2.3015</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4593</v>
+        <v>-2.8377</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3999</v>
+        <v>0.5362</v>
       </c>
       <c r="G12" t="n">
         <v>1.5004</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0673</v>
+        <v>0.6906</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5933</v>
+        <v>0.0283</v>
       </c>
       <c r="U12" t="n">
-        <v>0.526</v>
+        <v>0.6623</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6119</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>33.0385</v>
+        <v>33.94690000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>19.0608</v>
+        <v>19.9694</v>
       </c>
       <c r="F13" t="n">
-        <v>13.9777</v>
+        <v>13.9775</v>
       </c>
       <c r="G13" t="n">
         <v>26.7226</v>
@@ -1441,7 +1441,7 @@
         <v>21.0214</v>
       </c>
       <c r="J13" t="n">
-        <v>26.3253</v>
+        <v>26.32530000000001</v>
       </c>
       <c r="K13" t="n">
         <v>10.5869</v>
@@ -1450,13 +1450,13 @@
         <v>15.7387</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3971000000000001</v>
+        <v>0.3971</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.885800000000001</v>
+        <v>-4.8858</v>
       </c>
       <c r="O13" t="n">
-        <v>5.283</v>
+        <v>5.283000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-2.910499999999999</v>
@@ -1468,13 +1468,13 @@
         <v>13.5824</v>
       </c>
       <c r="S13" t="n">
-        <v>8.0025</v>
+        <v>8.9108</v>
       </c>
       <c r="T13" t="n">
-        <v>3.347699999999999</v>
+        <v>4.2562</v>
       </c>
       <c r="U13" t="n">
-        <v>4.654699999999999</v>
+        <v>4.6545</v>
       </c>
       <c r="V13" t="n">
         <v>1.2239</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0582</v>
+        <v>-0.6612</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7577</v>
+        <v>2.4574</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.8159</v>
+        <v>-3.1185</v>
       </c>
       <c r="G14" t="n">
         <v>-4.6557</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3273</v>
+        <v>-0.2756</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3489</v>
+        <v>-0.6492</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6761</v>
+        <v>0.3735</v>
       </c>
       <c r="V14" t="n">
         <v>1.5537</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BUHORSKYI</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.5568</v>
+        <v>-1.2653</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9164</v>
+        <v>0.061</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4732</v>
+        <v>-1.3263</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.3913</v>
+        <v>1.3618</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1129</v>
+        <v>3.7915</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.2785</v>
+        <v>-2.4297</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1683</v>
+        <v>3.5325</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1277</v>
+        <v>4.1771</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0406</v>
+        <v>-0.6445</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5596</v>
+        <v>-2.1708</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2406</v>
+        <v>-0.3856</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3191</v>
+        <v>-1.7852</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0476</v>
+        <v>-1.3554</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1839</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2315</v>
+        <v>-0.4839</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2821</v>
+        <v>-1.2716</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5642</v>
+        <v>-0.6597</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8462</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>D. BUHORSKYI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7719</v>
+        <v>-1.9393</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3394</v>
+        <v>0.3158</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4325</v>
+        <v>-2.2551</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3618</v>
+        <v>-2.3913</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7915</v>
+        <v>-0.1129</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.4297</v>
+        <v>-2.2785</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5325</v>
+        <v>0.1683</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1771</v>
+        <v>0.1277</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6445</v>
+        <v>0.0406</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1708</v>
+        <v>-2.5596</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3856</v>
+        <v>-0.2406</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7852</v>
+        <v>-2.3191</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.862</v>
+        <v>-0.4301</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2719</v>
+        <v>-0.4167</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5901</v>
+        <v>-0.0134</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2716</v>
+        <v>-0.2821</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6597</v>
+        <v>0.5642</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6119</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9181</v>
+        <v>-1.966</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2403</v>
+        <v>-1.0401</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6777</v>
+        <v>-0.9258</v>
       </c>
       <c r="G17" t="n">
         <v>-5.0252</v>
@@ -1780,13 +1780,13 @@
         <v>2.7164</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0973</v>
+        <v>-0.1452</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6528</v>
+        <v>-0.4526</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5554</v>
+        <v>0.3073</v>
       </c>
       <c r="V17" t="n">
         <v>1.4582</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3879</v>
+        <v>-3.2911</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5613</v>
+        <v>-0.7615</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8266</v>
+        <v>-2.5296</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2495</v>
@@ -1858,13 +1858,13 @@
         <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0787</v>
+        <v>-0.9819</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0471</v>
+        <v>-0.2473</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0316</v>
+        <v>-0.7346</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6401</v>
+        <v>-3.4855</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0479</v>
+        <v>-1.9478</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5922</v>
+        <v>-1.5377</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1314</v>
@@ -1936,13 +1936,13 @@
         <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5088</v>
+        <v>-0.3541</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4722</v>
+        <v>-0.3721</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0366</v>
+        <v>0.0179</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7769</v>
+        <v>-3.5984</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0145</v>
+        <v>-1.2147</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7624</v>
+        <v>-2.3837</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7313</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7039</v>
+        <v>-1.5253</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4229</v>
+        <v>-0.6231</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.281</v>
+        <v>-0.9023</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.1434</v>
+        <v>-7.9888</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.2357</v>
+        <v>-5.1356</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9077</v>
+        <v>-2.8532</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2679</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2367</v>
+        <v>-1.082</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7268</v>
+        <v>-0.6267</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5099</v>
+        <v>-0.4553</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5642</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.785</v>
+        <v>-8.1755</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.2125</v>
+        <v>-6.712</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5725</v>
+        <v>-1.4634</v>
       </c>
       <c r="G22" t="n">
         <v>-4.632</v>
@@ -2170,13 +2170,13 @@
         <v>2.1344</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7947</v>
+        <v>-1.1852</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8962</v>
+        <v>-0.3957</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8986</v>
+        <v>-0.7896</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6119</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-33.0383</v>
+        <v>-32.3711</v>
       </c>
       <c r="E23" t="n">
         <v>-13.9775</v>
       </c>
       <c r="F23" t="n">
-        <v>-19.0607</v>
+        <v>-18.3933</v>
       </c>
       <c r="G23" t="n">
         <v>-26.7225</v>
@@ -2224,7 +2224,7 @@
         <v>-0.3971999999999998</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8857</v>
+        <v>4.885700000000001</v>
       </c>
       <c r="L23" t="n">
         <v>-5.283</v>
@@ -2248,13 +2248,13 @@
         <v>16.4927</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.002400000000002</v>
+        <v>-7.3348</v>
       </c>
       <c r="T23" t="n">
         <v>-4.6549</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.3478</v>
+        <v>-2.6804</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
